--- a/Result/profitability/8110.xlsx
+++ b/Result/profitability/8110.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34375</v>
+        <v>0.61625</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5425</v>
+        <v>6.17125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.38125</v>
+        <v>0.6537500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>6.335</v>
+        <v>6.567499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42125</v>
+        <v>0.6575</v>
       </c>
       <c r="N4" t="n">
-        <v>6.571249999999999</v>
+        <v>7.55875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.36375</v>
+        <v>0.7074999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2825</v>
+        <v>7.66125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.44625</v>
+        <v>0.49375</v>
       </c>
       <c r="N6" t="n">
-        <v>6.415</v>
+        <v>7.08875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.235</v>
+        <v>0.34875</v>
       </c>
       <c r="N7" t="n">
-        <v>7.08625</v>
+        <v>7.09625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1075</v>
+        <v>0.30875</v>
       </c>
       <c r="N8" t="n">
-        <v>7.290000000000001</v>
+        <v>7.1725</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.07625</v>
       </c>
       <c r="N9" t="n">
-        <v>7.194999999999999</v>
+        <v>7.195</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1766</v>
+      </c>
+      <c r="E75" t="n">
+        <v>177</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1098</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1102</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.306249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9399999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09362549800796804</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.230769230769231</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-5.715025906735751</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
